--- a/all_sim/gpt_domain.xlsx
+++ b/all_sim/gpt_domain.xlsx
@@ -331,16 +331,16 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="36.300000000000004" min="1" max="1" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="2" max="2" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="5" max="5" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="6" max="6" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="7" max="7" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="8" max="8" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="2" max="2" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="3" max="3" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="5" max="5" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="6" max="6" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="7" max="7" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="8" max="8" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="9" max="9" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="10" max="10" bestFit="1" customWidth="1"/>
-    <col width="26.400000000000002" min="11" max="11" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="10" max="10" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="11" max="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -350,34 +350,34 @@
         </is>
       </c>
       <c r="B1" s="0" t="n">
-        <v>0.9464285714285715</v>
+        <v>0.9732142857142858</v>
       </c>
       <c r="C1" s="0" t="n">
-        <v>0.055059523809523815</v>
+        <v>0.5275297619047619</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.03645833333333334</v>
+        <v>0.5182291666666666</v>
       </c>
       <c r="E1" s="0" t="n">
-        <v>0.03645833333333334</v>
+        <v>0.5182291666666666</v>
       </c>
       <c r="F1" s="0" t="n">
-        <v>0.03645833333333334</v>
+        <v>0.5182291666666666</v>
       </c>
       <c r="G1" s="0" t="n">
-        <v>0.03645833333333334</v>
+        <v>0.5182291666666666</v>
       </c>
       <c r="H1" s="0" t="n">
-        <v>0.03645833333333334</v>
+        <v>0.5182291666666666</v>
       </c>
       <c r="I1" s="0" t="n">
-        <v>0.03645833333333334</v>
+        <v>0.5182291666666666</v>
       </c>
       <c r="J1" s="0" t="n">
-        <v>0.03645833333333334</v>
+        <v>0.5182291666666666</v>
       </c>
       <c r="K1" s="0" t="n">
-        <v>0.03645833333333334</v>
+        <v>0.5182291666666666</v>
       </c>
     </row>
     <row r="2">
@@ -387,34 +387,34 @@
         </is>
       </c>
       <c r="B2" s="0" t="n">
-        <v>0.2392857142857143</v>
+        <v>0.5258928571428572</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>0.21428571428571427</v>
+        <v>0.4942396313364055</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.21428571428571427</v>
+        <v>0.4942396313364055</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>0.21428571428571427</v>
+        <v>0.4942396313364055</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>0.21428571428571427</v>
+        <v>0.4942396313364055</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>0.21428571428571427</v>
+        <v>0.4942396313364055</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>0.05952380952380952</v>
+        <v>0.415007806401249</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>0.05952380952380952</v>
+        <v>0.415007806401249</v>
       </c>
       <c r="J2" s="0" t="n">
-        <v>0.05952380952380952</v>
+        <v>0.415007806401249</v>
       </c>
       <c r="K2" s="0" t="n">
-        <v>0.05952380952380952</v>
+        <v>0.415007806401249</v>
       </c>
     </row>
     <row r="3">
@@ -424,34 +424,34 @@
         </is>
       </c>
       <c r="B3" s="0" t="n">
-        <v>0.8690476190476191</v>
+        <v>0.9345238095238095</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>0.8690476190476191</v>
+        <v>0.9345238095238095</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>0.8690476190476191</v>
+        <v>0.9345238095238095</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>0.7261904761904763</v>
+        <v>0.8630952380952381</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>0.7261904761904763</v>
+        <v>0.8630952380952381</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>0.5285714285714286</v>
+        <v>0.7642857142857142</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>0.5285714285714286</v>
+        <v>0.7642857142857142</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>0.5285714285714286</v>
+        <v>0.7642857142857142</v>
       </c>
       <c r="J3" s="0" t="n">
-        <v>0.5285714285714286</v>
+        <v>0.7642857142857142</v>
       </c>
       <c r="K3" s="0" t="n">
-        <v>0.5285714285714286</v>
+        <v>0.7642857142857142</v>
       </c>
     </row>
     <row r="4">
@@ -464,31 +464,31 @@
         <v>1.0</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>0.875</v>
+        <v>0.9375</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.875</v>
+        <v>0.9375</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>0.875</v>
+        <v>0.9375</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>1.0</v>
       </c>
       <c r="G4" s="0" t="n">
-        <v>0.875</v>
+        <v>0.9375</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>0.875</v>
+        <v>0.9375</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>0.875</v>
+        <v>0.9375</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>0.875</v>
+        <v>0.9375</v>
       </c>
       <c r="K4" s="0" t="n">
-        <v>0.875</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="5">
@@ -498,34 +498,34 @@
         </is>
       </c>
       <c r="B5" s="0" t="n">
-        <v>0.7266666666666668</v>
+        <v>0.8633333333333334</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>0.6055555555555556</v>
+        <v>0.8027777777777778</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.6055555555555556</v>
+        <v>0.8027777777777778</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>0.59375</v>
+        <v>0.7484879032258065</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>0.5666666666666668</v>
+        <v>0.75</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>0.35</v>
+        <v>0.64375</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>0.35</v>
+        <v>0.64375</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>0.35</v>
+        <v>0.64375</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>0.35</v>
+        <v>0.64375</v>
       </c>
       <c r="K5" s="0" t="n">
-        <v>0.35</v>
+        <v>0.64375</v>
       </c>
     </row>
     <row r="6">
@@ -538,31 +538,31 @@
         <v>1.0</v>
       </c>
       <c r="C6" s="0" t="n">
+        <v>0.8714285714285714</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>0.8580357142857142</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0.7071428571428572</v>
+      </c>
+      <c r="F6" s="0" t="n">
         <v>0.7428571428571429</v>
       </c>
-      <c r="D6" s="0" t="n">
-        <v>0.7160714285714286</v>
-      </c>
-      <c r="E6" s="0" t="n">
-        <v>0.4142857142857143</v>
-      </c>
-      <c r="F6" s="0" t="n">
-        <v>0.4857142857142857</v>
-      </c>
       <c r="G6" s="0" t="n">
-        <v>0.4142857142857143</v>
+        <v>0.7071428571428572</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>0.4857142857142857</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>0.4142857142857143</v>
+        <v>0.7071428571428572</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>0.4142857142857143</v>
+        <v>0.7071428571428572</v>
       </c>
       <c r="K6" s="0" t="n">
-        <v>0.4142857142857143</v>
+        <v>0.7071428571428572</v>
       </c>
     </row>
     <row r="7">
@@ -572,34 +572,34 @@
         </is>
       </c>
       <c r="B7" s="0" t="n">
-        <v>0.32936507936507936</v>
+        <v>0.6037069299264421</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>0.21180555555555558</v>
+        <v>0.4123543906810036</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.21969696969696972</v>
+        <v>0.460725677830941</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>0.14097222222222222</v>
+        <v>0.4684452947845805</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>0.09280303030303032</v>
+        <v>0.46476886209029067</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>0.13690476190476192</v>
+        <v>0.48890692640692646</v>
       </c>
       <c r="H7" s="0" t="n">
-        <v>0.19907407407407407</v>
+        <v>0.5106481481481482</v>
       </c>
       <c r="I7" s="0" t="n">
-        <v>0.07833333333333334</v>
+        <v>0.44482704402515727</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>0.14444444444444446</v>
+        <v>0.49905149051490516</v>
       </c>
       <c r="K7" s="0" t="n">
-        <v>0.14444444444444446</v>
+        <v>0.49905149051490516</v>
       </c>
     </row>
     <row r="8">
@@ -609,34 +609,34 @@
         </is>
       </c>
       <c r="B8" s="0" t="n">
-        <v>0.9777777777777779</v>
+        <v>0.9888888888888889</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>0.525</v>
+        <v>0.7625</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.5160714285714286</v>
+        <v>0.7580357142857144</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>0.5160714285714286</v>
+        <v>0.7580357142857144</v>
       </c>
       <c r="F8" s="0" t="n">
-        <v>0.5160714285714286</v>
+        <v>0.7580357142857144</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>0.5160714285714286</v>
+        <v>0.7580357142857144</v>
       </c>
       <c r="H8" s="0" t="n">
-        <v>0.5160714285714286</v>
+        <v>0.7580357142857144</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>0.5160714285714286</v>
+        <v>0.7580357142857144</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>0.5160714285714286</v>
+        <v>0.7580357142857144</v>
       </c>
       <c r="K8" s="0" t="n">
-        <v>0.5160714285714286</v>
+        <v>0.7580357142857144</v>
       </c>
     </row>
     <row r="9">
@@ -652,28 +652,28 @@
         <v>1.0</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.8053571428571429</v>
+        <v>0.9026785714285714</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>0.8053571428571429</v>
+        <v>0.9026785714285714</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>0.8053571428571429</v>
+        <v>0.9026785714285714</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>0.6027777777777777</v>
+        <v>0.8013888888888889</v>
       </c>
       <c r="H9" s="0" t="n">
-        <v>0.8053571428571429</v>
+        <v>0.9026785714285714</v>
       </c>
       <c r="I9" s="0" t="n">
-        <v>0.8053571428571429</v>
+        <v>0.9026785714285714</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>0.8053571428571429</v>
+        <v>0.9026785714285714</v>
       </c>
       <c r="K9" s="0" t="n">
-        <v>0.8053571428571429</v>
+        <v>0.9026785714285714</v>
       </c>
     </row>
     <row r="10">
@@ -683,34 +683,34 @@
         </is>
       </c>
       <c r="B10" s="0" t="n">
-        <v>1.0</v>
+        <v>0.9838709677419355</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>1.0</v>
+        <v>0.9838709677419355</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>1.0</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>0.675</v>
+        <v>0.7517857142857143</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>0.625</v>
+        <v>0.7267857142857143</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>0.3298611111111111</v>
+        <v>0.5696924603174603</v>
       </c>
       <c r="H10" s="0" t="n">
-        <v>0.6875</v>
+        <v>0.7461890243902439</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>0.12361111111111112</v>
+        <v>0.39513888888888893</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>0.03580246913580247</v>
+        <v>0.3381259536690248</v>
       </c>
       <c r="K10" s="0" t="n">
-        <v>0.1283068783068783</v>
+        <v>0.5029289493575207</v>
       </c>
     </row>
     <row r="11">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="B11" s="0" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.5988888888888889</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.5988888888888889</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.04999999999999999</v>
+        <v>0.4865384615384616</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>0.04999999999999999</v>
+        <v>0.4865384615384616</v>
       </c>
       <c r="F11" s="0" t="n">
-        <v>0.04999999999999999</v>
+        <v>0.4865384615384616</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>0.04999999999999999</v>
+        <v>0.4865384615384616</v>
       </c>
       <c r="H11" s="0" t="n">
-        <v>0.04999999999999999</v>
+        <v>0.4865384615384616</v>
       </c>
       <c r="I11" s="0" t="n">
-        <v>0.04999999999999999</v>
+        <v>0.4865384615384616</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>0.04999999999999999</v>
+        <v>0.4865384615384616</v>
       </c>
       <c r="K11" s="0" t="n">
-        <v>0.04999999999999999</v>
+        <v>0.4865384615384616</v>
       </c>
     </row>
     <row r="12">
@@ -757,34 +757,34 @@
         </is>
       </c>
       <c r="B12" s="0" t="n">
-        <v>0.0997835497835498</v>
+        <v>0.5255015309893358</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>0.04365530303030304</v>
+        <v>0.4274880288736421</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.04365530303030304</v>
+        <v>0.4274880288736421</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>0.043258673693456304</v>
+        <v>0.36491291893628036</v>
       </c>
       <c r="F12" s="0" t="n">
-        <v>0.09882154882154882</v>
+        <v>0.4694107744107744</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>0.0994949494949495</v>
+        <v>0.4815656565656566</v>
       </c>
       <c r="H12" s="0" t="n">
-        <v>0.02408568443051202</v>
+        <v>0.330792842215256</v>
       </c>
       <c r="I12" s="0" t="n">
-        <v>0.00997722321251733</v>
+        <v>0.336383960443468</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>0.017154301637060256</v>
+        <v>0.34565580250392336</v>
       </c>
       <c r="K12" s="0" t="n">
-        <v>0.18207718207718207</v>
+        <v>0.5126072184895715</v>
       </c>
     </row>
     <row r="13">
@@ -794,34 +794,34 @@
         </is>
       </c>
       <c r="B13" s="0" t="n">
-        <v>1.0</v>
+        <v>0.9615384615384616</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>0.23905723905723905</v>
+        <v>0.5957190957190956</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>1.0</v>
+        <v>0.9615384615384616</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>1.0</v>
+        <v>0.9736842105263158</v>
       </c>
       <c r="F13" s="0" t="n">
-        <v>0.24579124579124578</v>
+        <v>0.5774410774410774</v>
       </c>
       <c r="G13" s="0" t="n">
-        <v>0.3367521367521367</v>
+        <v>0.6151845790143662</v>
       </c>
       <c r="H13" s="0" t="n">
-        <v>0.2679738562091503</v>
+        <v>0.5302133431989148</v>
       </c>
       <c r="I13" s="0" t="n">
-        <v>0.28215488215488216</v>
+        <v>0.5007265638844587</v>
       </c>
       <c r="J13" s="0" t="n">
-        <v>0.269281045751634</v>
+        <v>0.482098149994461</v>
       </c>
       <c r="K13" s="0" t="n">
-        <v>0.30518518518518517</v>
+        <v>0.5162289562289563</v>
       </c>
     </row>
     <row r="14">
@@ -831,34 +831,34 @@
         </is>
       </c>
       <c r="B14" s="0" t="n">
-        <v>0.9074074074074073</v>
+        <v>0.9102254428341385</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>0.6455026455026455</v>
+        <v>0.7671957671957672</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.49603174603174605</v>
+        <v>0.6948243836541709</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>0.49603174603174605</v>
+        <v>0.6948243836541709</v>
       </c>
       <c r="F14" s="0" t="n">
-        <v>0.49603174603174605</v>
+        <v>0.6948243836541709</v>
       </c>
       <c r="G14" s="0" t="n">
-        <v>0.49603174603174605</v>
+        <v>0.6948243836541709</v>
       </c>
       <c r="H14" s="0" t="n">
-        <v>0.6455026455026455</v>
+        <v>0.7671957671957672</v>
       </c>
       <c r="I14" s="0" t="n">
-        <v>0.6455026455026455</v>
+        <v>0.7671957671957672</v>
       </c>
       <c r="J14" s="0" t="n">
-        <v>0.6455026455026455</v>
+        <v>0.7671957671957672</v>
       </c>
       <c r="K14" s="0" t="n">
-        <v>0.3327380952380953</v>
+        <v>0.5189331501831502</v>
       </c>
     </row>
     <row r="15">
@@ -868,34 +868,34 @@
         </is>
       </c>
       <c r="B15" s="0" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.9538461538461538</v>
       </c>
       <c r="C15" s="0" t="n">
-        <v>0.2702380952380952</v>
+        <v>0.6222985347985348</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>0.2702380952380952</v>
+        <v>0.6222985347985348</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>0.20833333333333334</v>
+        <v>0.5803571428571428</v>
       </c>
       <c r="F15" s="0" t="n">
-        <v>0.19849537037037038</v>
+        <v>0.5411081503014643</v>
       </c>
       <c r="G15" s="0" t="n">
-        <v>0.19386574074074073</v>
+        <v>0.5413773148148148</v>
       </c>
       <c r="H15" s="0" t="n">
-        <v>0.1488715277777778</v>
+        <v>0.516296229005168</v>
       </c>
       <c r="I15" s="0" t="n">
-        <v>0.15643939393939393</v>
+        <v>0.4948863636363636</v>
       </c>
       <c r="J15" s="0" t="n">
-        <v>0.19895833333333335</v>
+        <v>0.5550347222222223</v>
       </c>
       <c r="K15" s="0" t="n">
-        <v>0.1326388888888889</v>
+        <v>0.4774305555555555</v>
       </c>
     </row>
     <row r="16">
@@ -908,31 +908,31 @@
         <v>1.0</v>
       </c>
       <c r="C16" s="0" t="n">
-        <v>0.5995370370370371</v>
+        <v>0.7858796296296297</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>0.4</v>
+        <v>0.5823529411764705</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>0.047619047619047616</v>
+        <v>0.3659147869674185</v>
       </c>
       <c r="F16" s="0" t="n">
-        <v>0.047619047619047616</v>
+        <v>0.3659147869674185</v>
       </c>
       <c r="G16" s="0" t="n">
-        <v>0.047619047619047616</v>
+        <v>0.3659147869674185</v>
       </c>
       <c r="H16" s="0" t="n">
-        <v>0.014961389961389961</v>
+        <v>0.30748069498069497</v>
       </c>
       <c r="I16" s="0" t="n">
-        <v>0.01368131868131868</v>
+        <v>0.30684065934065935</v>
       </c>
       <c r="J16" s="0" t="n">
-        <v>0.01368131868131868</v>
+        <v>0.30684065934065935</v>
       </c>
       <c r="K16" s="0" t="n">
-        <v>0.0068936877076411955</v>
+        <v>0.29756449091264414</v>
       </c>
     </row>
     <row r="17">
@@ -942,34 +942,34 @@
         </is>
       </c>
       <c r="B17" s="0" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="C17" s="0" t="n">
-        <v>0.6150793650793651</v>
+        <v>0.741750208855472</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>0.2392857142857143</v>
+        <v>0.5098867595818816</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>0.17994505494505494</v>
+        <v>0.5088914463914463</v>
       </c>
       <c r="F17" s="0" t="n">
-        <v>0.14891304347826087</v>
+        <v>0.43278985507246376</v>
       </c>
       <c r="G17" s="0" t="n">
-        <v>0.19679487179487182</v>
+        <v>0.45804655870445343</v>
       </c>
       <c r="H17" s="0" t="n">
-        <v>0.012949465500485908</v>
+        <v>0.33094281785662594</v>
       </c>
       <c r="I17" s="0" t="n">
-        <v>0.08412698412698413</v>
+        <v>0.4298185941043084</v>
       </c>
       <c r="J17" s="0" t="n">
-        <v>0.07708333333333334</v>
+        <v>0.4189764492753624</v>
       </c>
       <c r="K17" s="0" t="n">
-        <v>0.0880952380952381</v>
+        <v>0.42946428571428574</v>
       </c>
     </row>
     <row r="18">

--- a/all_sim/gpt_domain.xlsx
+++ b/all_sim/gpt_domain.xlsx
@@ -331,16 +331,16 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="36.300000000000004" min="1" max="1" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="2" max="2" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="2" max="2" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="3" max="3" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="4" max="4" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="5" max="5" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="6" max="6" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="7" max="7" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="8" max="8" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="9" max="9" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="10" max="10" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="11" max="11" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="8" max="8" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="9" max="9" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="10" max="10" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="11" max="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -350,34 +350,34 @@
         </is>
       </c>
       <c r="B1" s="0" t="n">
-        <v>0.9732142857142858</v>
+        <v>0.9464285714285715</v>
       </c>
       <c r="C1" s="0" t="n">
-        <v>0.5275297619047619</v>
+        <v>0.055059523809523815</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.5182291666666666</v>
+        <v>0.03645833333333334</v>
       </c>
       <c r="E1" s="0" t="n">
-        <v>0.5182291666666666</v>
+        <v>0.03645833333333334</v>
       </c>
       <c r="F1" s="0" t="n">
-        <v>0.5182291666666666</v>
+        <v>0.03645833333333334</v>
       </c>
       <c r="G1" s="0" t="n">
-        <v>0.5182291666666666</v>
+        <v>0.03645833333333334</v>
       </c>
       <c r="H1" s="0" t="n">
-        <v>0.5182291666666666</v>
+        <v>0.03645833333333334</v>
       </c>
       <c r="I1" s="0" t="n">
-        <v>0.5182291666666666</v>
+        <v>0.03645833333333334</v>
       </c>
       <c r="J1" s="0" t="n">
-        <v>0.5182291666666666</v>
+        <v>0.03645833333333334</v>
       </c>
       <c r="K1" s="0" t="n">
-        <v>0.5182291666666666</v>
+        <v>0.03645833333333334</v>
       </c>
     </row>
     <row r="2">
@@ -387,34 +387,34 @@
         </is>
       </c>
       <c r="B2" s="0" t="n">
-        <v>0.5258928571428572</v>
+        <v>0.19441964285714286</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>0.4942396313364055</v>
+        <v>0.1658986175115207</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.4942396313364055</v>
+        <v>0.1658986175115207</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>0.4942396313364055</v>
+        <v>0.1658986175115207</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>0.4942396313364055</v>
+        <v>0.1658986175115207</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>0.4942396313364055</v>
+        <v>0.1658986175115207</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>0.415007806401249</v>
+        <v>0.04586260733801717</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>0.415007806401249</v>
+        <v>0.04586260733801717</v>
       </c>
       <c r="J2" s="0" t="n">
-        <v>0.415007806401249</v>
+        <v>0.04586260733801717</v>
       </c>
       <c r="K2" s="0" t="n">
-        <v>0.415007806401249</v>
+        <v>0.04586260733801717</v>
       </c>
     </row>
     <row r="3">
@@ -424,34 +424,34 @@
         </is>
       </c>
       <c r="B3" s="0" t="n">
-        <v>0.9345238095238095</v>
+        <v>0.8690476190476191</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>0.9345238095238095</v>
+        <v>0.8690476190476191</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>0.9345238095238095</v>
+        <v>0.8690476190476191</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>0.8630952380952381</v>
+        <v>0.7261904761904763</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>0.8630952380952381</v>
+        <v>0.7261904761904763</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>0.7642857142857142</v>
+        <v>0.5285714285714286</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>0.7642857142857142</v>
+        <v>0.5285714285714286</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>0.7642857142857142</v>
+        <v>0.5285714285714286</v>
       </c>
       <c r="J3" s="0" t="n">
-        <v>0.7642857142857142</v>
+        <v>0.5285714285714286</v>
       </c>
       <c r="K3" s="0" t="n">
-        <v>0.7642857142857142</v>
+        <v>0.5285714285714286</v>
       </c>
     </row>
     <row r="4">
@@ -464,31 +464,31 @@
         <v>1.0</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>0.9375</v>
+        <v>0.875</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.9375</v>
+        <v>0.875</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>0.9375</v>
+        <v>0.875</v>
       </c>
       <c r="F4" s="0" t="n">
         <v>1.0</v>
       </c>
       <c r="G4" s="0" t="n">
-        <v>0.9375</v>
+        <v>0.875</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>0.9375</v>
+        <v>0.875</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>0.9375</v>
+        <v>0.875</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>0.9375</v>
+        <v>0.875</v>
       </c>
       <c r="K4" s="0" t="n">
-        <v>0.9375</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="5">
@@ -498,34 +498,34 @@
         </is>
       </c>
       <c r="B5" s="0" t="n">
-        <v>0.8633333333333334</v>
+        <v>0.7266666666666668</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>0.8027777777777778</v>
+        <v>0.6055555555555556</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.8027777777777778</v>
+        <v>0.6055555555555556</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>0.7484879032258065</v>
+        <v>0.5362903225806451</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>0.75</v>
+        <v>0.528888888888889</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>0.64375</v>
+        <v>0.328125</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>0.64375</v>
+        <v>0.328125</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>0.64375</v>
+        <v>0.328125</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>0.64375</v>
+        <v>0.328125</v>
       </c>
       <c r="K5" s="0" t="n">
-        <v>0.64375</v>
+        <v>0.328125</v>
       </c>
     </row>
     <row r="6">
@@ -538,31 +538,31 @@
         <v>1.0</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>0.8714285714285714</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0.8580357142857142</v>
+        <v>0.7160714285714286</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>0.7071428571428572</v>
+        <v>0.4142857142857143</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.4857142857142857</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>0.7071428571428572</v>
+        <v>0.4142857142857143</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.4857142857142857</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>0.7071428571428572</v>
+        <v>0.4142857142857143</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>0.7071428571428572</v>
+        <v>0.4142857142857143</v>
       </c>
       <c r="K6" s="0" t="n">
-        <v>0.7071428571428572</v>
+        <v>0.4142857142857143</v>
       </c>
     </row>
     <row r="7">
@@ -572,34 +572,34 @@
         </is>
       </c>
       <c r="B7" s="0" t="n">
-        <v>0.6037069299264421</v>
+        <v>0.289198606271777</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>0.4123543906810036</v>
+        <v>0.1298163082437276</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.460725677830941</v>
+        <v>0.1541733120680489</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>0.4684452947845805</v>
+        <v>0.11220238095238096</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>0.46476886209029067</v>
+        <v>0.07765151515151517</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>0.48890692640692646</v>
+        <v>0.1151244588744589</v>
       </c>
       <c r="H7" s="0" t="n">
-        <v>0.5106481481481482</v>
+        <v>0.16368312757201645</v>
       </c>
       <c r="I7" s="0" t="n">
-        <v>0.44482704402515727</v>
+        <v>0.06355345911949686</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>0.49905149051490516</v>
+        <v>0.12330623306233063</v>
       </c>
       <c r="K7" s="0" t="n">
-        <v>0.49905149051490516</v>
+        <v>0.12330623306233063</v>
       </c>
     </row>
     <row r="8">
@@ -609,34 +609,34 @@
         </is>
       </c>
       <c r="B8" s="0" t="n">
-        <v>0.9888888888888889</v>
+        <v>0.9777777777777779</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>0.7625</v>
+        <v>0.525</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.7580357142857144</v>
+        <v>0.5160714285714286</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>0.7580357142857144</v>
+        <v>0.5160714285714286</v>
       </c>
       <c r="F8" s="0" t="n">
-        <v>0.7580357142857144</v>
+        <v>0.5160714285714286</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>0.7580357142857144</v>
+        <v>0.5160714285714286</v>
       </c>
       <c r="H8" s="0" t="n">
-        <v>0.7580357142857144</v>
+        <v>0.5160714285714286</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>0.7580357142857144</v>
+        <v>0.5160714285714286</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>0.7580357142857144</v>
+        <v>0.5160714285714286</v>
       </c>
       <c r="K8" s="0" t="n">
-        <v>0.7580357142857144</v>
+        <v>0.5160714285714286</v>
       </c>
     </row>
     <row r="9">
@@ -652,28 +652,28 @@
         <v>1.0</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.9026785714285714</v>
+        <v>0.8053571428571429</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>0.9026785714285714</v>
+        <v>0.8053571428571429</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>0.9026785714285714</v>
+        <v>0.8053571428571429</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>0.8013888888888889</v>
+        <v>0.6027777777777777</v>
       </c>
       <c r="H9" s="0" t="n">
-        <v>0.9026785714285714</v>
+        <v>0.8053571428571429</v>
       </c>
       <c r="I9" s="0" t="n">
-        <v>0.9026785714285714</v>
+        <v>0.8053571428571429</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>0.9026785714285714</v>
+        <v>0.8053571428571429</v>
       </c>
       <c r="K9" s="0" t="n">
-        <v>0.9026785714285714</v>
+        <v>0.8053571428571429</v>
       </c>
     </row>
     <row r="10">
@@ -683,34 +683,34 @@
         </is>
       </c>
       <c r="B10" s="0" t="n">
-        <v>0.9838709677419355</v>
+        <v>0.967741935483871</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>0.9838709677419355</v>
+        <v>0.967741935483871</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>0.7517857142857143</v>
+        <v>0.5592857142857143</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>0.7267857142857143</v>
+        <v>0.5178571428571428</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>0.5696924603174603</v>
+        <v>0.26703042328042326</v>
       </c>
       <c r="H10" s="0" t="n">
-        <v>0.7461890243902439</v>
+        <v>0.5533536585365854</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>0.39513888888888893</v>
+        <v>0.08240740740740742</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>0.3381259536690248</v>
+        <v>0.022929671244277985</v>
       </c>
       <c r="K10" s="0" t="n">
-        <v>0.5029289493575207</v>
+        <v>0.1125958319835871</v>
       </c>
     </row>
     <row r="11">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="B11" s="0" t="n">
-        <v>0.5988888888888889</v>
+        <v>0.2555555555555556</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>0.5988888888888889</v>
+        <v>0.2555555555555556</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.4865384615384616</v>
+        <v>0.04615384615384615</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>0.4865384615384616</v>
+        <v>0.04615384615384615</v>
       </c>
       <c r="F11" s="0" t="n">
-        <v>0.4865384615384616</v>
+        <v>0.04615384615384615</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>0.4865384615384616</v>
+        <v>0.04615384615384615</v>
       </c>
       <c r="H11" s="0" t="n">
-        <v>0.4865384615384616</v>
+        <v>0.04615384615384615</v>
       </c>
       <c r="I11" s="0" t="n">
-        <v>0.4865384615384616</v>
+        <v>0.04615384615384615</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>0.4865384615384616</v>
+        <v>0.04615384615384615</v>
       </c>
       <c r="K11" s="0" t="n">
-        <v>0.4865384615384616</v>
+        <v>0.04615384615384615</v>
       </c>
     </row>
     <row r="12">
@@ -757,34 +757,34 @@
         </is>
       </c>
       <c r="B12" s="0" t="n">
-        <v>0.5255015309893358</v>
+        <v>0.09491605955020589</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>0.4274880288736421</v>
+        <v>0.035418453401943974</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>0.4274880288736421</v>
+        <v>0.035418453401943974</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>0.36491291893628036</v>
+        <v>0.02969998492386552</v>
       </c>
       <c r="F12" s="0" t="n">
-        <v>0.4694107744107744</v>
+        <v>0.083010101010101</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>0.4815656565656566</v>
+        <v>0.08592745638200185</v>
       </c>
       <c r="H12" s="0" t="n">
-        <v>0.330792842215256</v>
+        <v>0.015354623824451413</v>
       </c>
       <c r="I12" s="0" t="n">
-        <v>0.336383960443468</v>
+        <v>0.006612810733877766</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>0.34565580250392336</v>
+        <v>0.01156469773284961</v>
       </c>
       <c r="K12" s="0" t="n">
-        <v>0.5126072184895715</v>
+        <v>0.15351605547683977</v>
       </c>
     </row>
     <row r="13">
@@ -794,34 +794,34 @@
         </is>
       </c>
       <c r="B13" s="0" t="n">
-        <v>0.9615384615384616</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>0.5957190957190956</v>
+        <v>0.22767356100689431</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.9615384615384616</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>0.9736842105263158</v>
+        <v>0.9473684210526316</v>
       </c>
       <c r="F13" s="0" t="n">
-        <v>0.5774410774410774</v>
+        <v>0.2234465870829507</v>
       </c>
       <c r="G13" s="0" t="n">
-        <v>0.6151845790143662</v>
+        <v>0.3009274413529732</v>
       </c>
       <c r="H13" s="0" t="n">
-        <v>0.5302133431989148</v>
+        <v>0.21235664076951535</v>
       </c>
       <c r="I13" s="0" t="n">
-        <v>0.5007265638844587</v>
+        <v>0.20295351172544154</v>
       </c>
       <c r="J13" s="0" t="n">
-        <v>0.482098149994461</v>
+        <v>0.1871275063697795</v>
       </c>
       <c r="K13" s="0" t="n">
-        <v>0.5162289562289563</v>
+        <v>0.22195286195286196</v>
       </c>
     </row>
     <row r="14">
@@ -831,34 +831,34 @@
         </is>
       </c>
       <c r="B14" s="0" t="n">
-        <v>0.9102254428341385</v>
+        <v>0.8285024154589372</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>0.7671957671957672</v>
+        <v>0.5737801293356848</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.6948243836541709</v>
+        <v>0.4432624113475177</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>0.6948243836541709</v>
+        <v>0.4432624113475177</v>
       </c>
       <c r="F14" s="0" t="n">
-        <v>0.6948243836541709</v>
+        <v>0.4432624113475177</v>
       </c>
       <c r="G14" s="0" t="n">
-        <v>0.6948243836541709</v>
+        <v>0.4432624113475177</v>
       </c>
       <c r="H14" s="0" t="n">
-        <v>0.7671957671957672</v>
+        <v>0.5737801293356848</v>
       </c>
       <c r="I14" s="0" t="n">
-        <v>0.7671957671957672</v>
+        <v>0.5737801293356848</v>
       </c>
       <c r="J14" s="0" t="n">
-        <v>0.7671957671957672</v>
+        <v>0.5737801293356848</v>
       </c>
       <c r="K14" s="0" t="n">
-        <v>0.5189331501831502</v>
+        <v>0.23462301587301587</v>
       </c>
     </row>
     <row r="15">
@@ -868,34 +868,34 @@
         </is>
       </c>
       <c r="B15" s="0" t="n">
-        <v>0.9538461538461538</v>
+        <v>0.9094017094017093</v>
       </c>
       <c r="C15" s="0" t="n">
-        <v>0.6222985347985348</v>
+        <v>0.26330891330891326</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>0.6222985347985348</v>
+        <v>0.26330891330891326</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>0.5803571428571428</v>
+        <v>0.1984126984126984</v>
       </c>
       <c r="F15" s="0" t="n">
-        <v>0.5411081503014643</v>
+        <v>0.17541451335055988</v>
       </c>
       <c r="G15" s="0" t="n">
-        <v>0.5413773148148148</v>
+        <v>0.17232510288065842</v>
       </c>
       <c r="H15" s="0" t="n">
-        <v>0.516296229005168</v>
+        <v>0.1315608850129199</v>
       </c>
       <c r="I15" s="0" t="n">
-        <v>0.4948863636363636</v>
+        <v>0.13036616161616163</v>
       </c>
       <c r="J15" s="0" t="n">
-        <v>0.5550347222222223</v>
+        <v>0.18127314814814816</v>
       </c>
       <c r="K15" s="0" t="n">
-        <v>0.4774305555555555</v>
+        <v>0.10905864197530864</v>
       </c>
     </row>
     <row r="16">
@@ -908,31 +908,31 @@
         <v>1.0</v>
       </c>
       <c r="C16" s="0" t="n">
-        <v>0.7858796296296297</v>
+        <v>0.582883230452675</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>0.5823529411764705</v>
+        <v>0.3058823529411765</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>0.3659147869674185</v>
+        <v>0.03258145363408521</v>
       </c>
       <c r="F16" s="0" t="n">
-        <v>0.3659147869674185</v>
+        <v>0.03258145363408521</v>
       </c>
       <c r="G16" s="0" t="n">
-        <v>0.3659147869674185</v>
+        <v>0.03258145363408521</v>
       </c>
       <c r="H16" s="0" t="n">
-        <v>0.30748069498069497</v>
+        <v>0.008976833976833977</v>
       </c>
       <c r="I16" s="0" t="n">
-        <v>0.30684065934065935</v>
+        <v>0.008208791208791208</v>
       </c>
       <c r="J16" s="0" t="n">
-        <v>0.30684065934065935</v>
+        <v>0.008208791208791208</v>
       </c>
       <c r="K16" s="0" t="n">
-        <v>0.29756449091264414</v>
+        <v>0.004055110416259527</v>
       </c>
     </row>
     <row r="17">
@@ -942,34 +942,34 @@
         </is>
       </c>
       <c r="B17" s="0" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.5925925925925927</v>
       </c>
       <c r="C17" s="0" t="n">
-        <v>0.741750208855472</v>
+        <v>0.5341478696741855</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>0.5098867595818816</v>
+        <v>0.1867595818815331</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>0.5088914463914463</v>
+        <v>0.15076477576477576</v>
       </c>
       <c r="F17" s="0" t="n">
-        <v>0.43278985507246376</v>
+        <v>0.10672101449275362</v>
       </c>
       <c r="G17" s="0" t="n">
-        <v>0.45804655870445343</v>
+        <v>0.14155420602789026</v>
       </c>
       <c r="H17" s="0" t="n">
-        <v>0.33094281785662594</v>
+        <v>0.008403376548187664</v>
       </c>
       <c r="I17" s="0" t="n">
-        <v>0.4298185941043084</v>
+        <v>0.06524133462908974</v>
       </c>
       <c r="J17" s="0" t="n">
-        <v>0.4189764492753624</v>
+        <v>0.05865036231884058</v>
       </c>
       <c r="K17" s="0" t="n">
-        <v>0.42946428571428574</v>
+        <v>0.06790674603174604</v>
       </c>
     </row>
     <row r="18">
